--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
   <si>
     <t>#</t>
   </si>
@@ -25,9 +25,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>测试说明</t>
-  </si>
-  <si>
     <t>名字</t>
   </si>
   <si>
@@ -43,23 +40,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>测试技能1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试技能2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>测试技能3</t>
-  </si>
-  <si>
-    <t>测试技能4</t>
-  </si>
-  <si>
-    <t>测试技能5</t>
-  </si>
-  <si>
     <t>Name</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -78,6 +58,34 @@
   </si>
   <si>
     <t>技能名字5</t>
+  </si>
+  <si>
+    <t>目标选择方式</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>selectType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>目标选择参数</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelectParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>sharptype</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -449,27 +457,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:G10"/>
+  <dimension ref="C1:H10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="5" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="28.75" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="E2" s="2" t="s">
+    <row r="1" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="G1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="3:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -480,43 +490,56 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="F4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>6600001</v>
       </c>
@@ -526,11 +549,10 @@
       <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>6600002</v>
       </c>
@@ -540,11 +562,10 @@
       <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>6600003</v>
       </c>
@@ -554,11 +575,10 @@
       <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>6600004</v>
       </c>
@@ -568,11 +588,10 @@
       <c r="E9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>6600005</v>
       </c>
@@ -582,9 +601,8 @@
       <c r="E10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>#</t>
   </si>
@@ -64,10 +64,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>selectType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -80,11 +76,19 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>string[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>sharptype</t>
+    <t>SelectType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shapetype</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3000,3,1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -471,7 +475,7 @@
   <sheetData>
     <row r="1" spans="3:8" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="3:8" x14ac:dyDescent="0.3">
@@ -493,7 +497,7 @@
         <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>4</v>
@@ -510,10 +514,10 @@
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>5</v>
@@ -530,10 +534,10 @@
         <v>7</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>7</v>
@@ -549,8 +553,12 @@
       <c r="E6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
@@ -562,8 +570,12 @@
       <c r="E7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
+      <c r="F7" s="1">
+        <v>2</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
@@ -575,8 +587,12 @@
       <c r="E8" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
@@ -588,8 +604,12 @@
       <c r="E9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
+      <c r="F9" s="1">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
@@ -601,8 +621,12 @@
       <c r="E10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>#</t>
   </si>
@@ -89,6 +89,14 @@
   </si>
   <si>
     <t>1,3000,3,1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>通知客户端类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NoticeClientType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -461,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:H10"/>
+  <dimension ref="C1:I10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -470,20 +478,21 @@
     <col min="5" max="6" width="9.625" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.75" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:9" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:9" x14ac:dyDescent="0.3">
       <c r="H2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -502,8 +511,11 @@
       <c r="H3" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I3" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -522,8 +534,11 @@
       <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -542,8 +557,11 @@
       <c r="H5" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>6600001</v>
       </c>
@@ -559,8 +577,11 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>6600002</v>
       </c>
@@ -576,8 +597,11 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>6600003</v>
       </c>
@@ -593,8 +617,11 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>6600004</v>
       </c>
@@ -610,8 +637,11 @@
       <c r="G9" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>6600005</v>
       </c>
@@ -625,6 +655,9 @@
         <v>3</v>
       </c>
       <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
         <v>0</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>#</t>
   </si>
@@ -97,6 +97,26 @@
   </si>
   <si>
     <t>NoticeClientType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中目标时间点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitActionTimes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中自身时间点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitActionTimes</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -469,7 +489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:I10"/>
+  <dimension ref="C1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -478,21 +498,21 @@
     <col min="5" max="6" width="9.625" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="2"/>
+    <col min="9" max="11" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:11" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:11" x14ac:dyDescent="0.3">
       <c r="H2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -514,8 +534,14 @@
       <c r="I3" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -537,8 +563,14 @@
       <c r="I4" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="J4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -560,8 +592,14 @@
       <c r="I5" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="J5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>6600001</v>
       </c>
@@ -580,8 +618,14 @@
       <c r="I6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>6600002</v>
       </c>
@@ -600,8 +644,14 @@
       <c r="I7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>6600003</v>
       </c>
@@ -620,8 +670,14 @@
       <c r="I8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>6600004</v>
       </c>
@@ -640,8 +696,14 @@
       <c r="I9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:11" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>6600005</v>
       </c>
@@ -658,6 +720,12 @@
         <v>0</v>
       </c>
       <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>#</t>
   </si>
@@ -117,6 +117,14 @@
   </si>
   <si>
     <t>SelfHitActionTimes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能总时长</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalTime</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -489,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:K10"/>
+  <dimension ref="C1:L10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -498,21 +506,21 @@
     <col min="5" max="6" width="9.625" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.75" style="2" customWidth="1"/>
-    <col min="9" max="11" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="9" max="12" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:12" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:12" x14ac:dyDescent="0.3">
       <c r="H2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -540,8 +548,11 @@
       <c r="K3" s="3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="L3" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -569,8 +580,11 @@
       <c r="K4" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="L4" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -598,8 +612,11 @@
       <c r="K5" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="L5" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>6600001</v>
       </c>
@@ -624,8 +641,11 @@
       <c r="K6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>6600002</v>
       </c>
@@ -650,8 +670,11 @@
       <c r="K7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>6600003</v>
       </c>
@@ -676,8 +699,11 @@
       <c r="K8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>6600004</v>
       </c>
@@ -702,8 +728,11 @@
       <c r="K9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.3">
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>6600005</v>
       </c>
@@ -726,6 +755,9 @@
         <v>0</v>
       </c>
       <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
         <v>0</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
   <si>
     <t>#</t>
   </si>
@@ -125,6 +125,22 @@
   </si>
   <si>
     <t>TotalTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中行为</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中自身行为</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitAction</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -497,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:L10"/>
+  <dimension ref="C1:N10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -506,21 +522,21 @@
     <col min="5" max="6" width="9.625" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.75" style="2" customWidth="1"/>
-    <col min="9" max="12" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="9" max="14" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:14" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:14" x14ac:dyDescent="0.3">
       <c r="H2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -543,16 +559,22 @@
         <v>22</v>
       </c>
       <c r="J3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -575,16 +597,22 @@
         <v>23</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -607,16 +635,22 @@
         <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="L5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>6600001</v>
       </c>
@@ -635,17 +669,15 @@
       <c r="I6" s="1">
         <v>0</v>
       </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>6600002</v>
       </c>
@@ -664,17 +696,15 @@
       <c r="I7" s="1">
         <v>0</v>
       </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>6600003</v>
       </c>
@@ -693,17 +723,15 @@
       <c r="I8" s="1">
         <v>0</v>
       </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>6600004</v>
       </c>
@@ -722,17 +750,15 @@
       <c r="I9" s="1">
         <v>0</v>
       </c>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.3">
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>6600005</v>
       </c>
@@ -751,13 +777,11 @@
       <c r="I10" s="1">
         <v>0</v>
       </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1">
         <v>0</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t>#</t>
   </si>
@@ -141,6 +141,26 @@
   </si>
   <si>
     <t>SelfHitAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中Buff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitBuffs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中自身Buff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitBuffs</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -513,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:N10"/>
+  <dimension ref="C1:P10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -522,21 +542,23 @@
     <col min="5" max="6" width="9.625" style="2" customWidth="1"/>
     <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28.75" style="2" customWidth="1"/>
-    <col min="9" max="14" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="9" max="13" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.25" style="2" customWidth="1"/>
+    <col min="16" max="16" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:16" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:16" x14ac:dyDescent="0.3">
       <c r="H2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -571,10 +593,16 @@
         <v>27</v>
       </c>
       <c r="N3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -609,10 +637,16 @@
         <v>28</v>
       </c>
       <c r="N4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -647,10 +681,16 @@
         <v>26</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>6600001</v>
       </c>
@@ -673,11 +713,13 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>6600002</v>
       </c>
@@ -700,11 +742,13 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>6600003</v>
       </c>
@@ -727,11 +771,13 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>6600004</v>
       </c>
@@ -754,11 +800,13 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:16" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>6600005</v>
       </c>
@@ -781,7 +829,9 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10" s="1">
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1">
         <v>0</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
   <si>
     <t>#</t>
   </si>
@@ -68,99 +68,103 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>目标选择参数</t>
+    <t>SelectType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>shapetype</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,3000,3,1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>通知客户端类型</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NoticeClientType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中目标时间点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitActionTimes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中自身时间点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitActionTimes</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能总时长</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TotalTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中行为</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中自身行为</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitAction</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中Buff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitBuffs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中自身Buff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitBuffs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShapeParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>形状</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>SelectParam</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SelectType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>shapetype</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>1,3000,3,1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>通知客户端类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>NoticeClientType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能命中目标时间点</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HitActionTimes</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能命中自身时间点</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SelfHitActionTimes</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能总时长</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TotalTime</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>命中行为</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HitAction</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>命中自身行为</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SelfHitAction</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>命中Buff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>HitBuffs</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>int[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>命中自身Buff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SelfHitBuffs</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -533,32 +537,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:P10"/>
+  <dimension ref="C1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
     <col min="5" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="28.75" style="2" customWidth="1"/>
-    <col min="9" max="13" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.25" style="2" customWidth="1"/>
-    <col min="16" max="16" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="2"/>
+    <col min="7" max="8" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.75" style="2" customWidth="1"/>
+    <col min="10" max="14" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="15.25" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:17" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="H2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="3:16" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="I2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -572,37 +579,40 @@
         <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="N3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="P3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="3:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -613,40 +623,43 @@
         <v>8</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="N4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="P4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="3:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -660,37 +673,40 @@
         <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="K5" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="3:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>6600001</v>
       </c>
@@ -703,23 +719,24 @@
       <c r="F6" s="1">
         <v>0</v>
       </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>6600002</v>
       </c>
@@ -733,22 +750,25 @@
         <v>2</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1"/>
+        <v>5000</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>6600003</v>
       </c>
@@ -762,22 +782,25 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1"/>
+        <v>5000</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>6600004</v>
       </c>
@@ -790,23 +813,26 @@
       <c r="F9" s="1">
         <v>2</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1"/>
+      <c r="G9" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>6600005</v>
       </c>
@@ -820,18 +846,21 @@
         <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1"/>
+        <v>5000</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
-      <c r="P10" s="1">
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1">
         <v>0</v>
       </c>
     </row>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
   <si>
     <t>#</t>
   </si>
@@ -165,6 +165,22 @@
   </si>
   <si>
     <t>SelectParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>selectParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,3000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>77001,77001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,200</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -229,13 +245,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -546,7 +567,8 @@
     <col min="5" max="6" width="9.625" style="2" customWidth="1"/>
     <col min="7" max="8" width="11" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.75" style="2" customWidth="1"/>
-    <col min="10" max="14" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="15.25" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="15.25" style="2" customWidth="1"/>
     <col min="17" max="17" width="15.25" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9" style="2"/>
@@ -554,10 +576,13 @@
   <sheetData>
     <row r="1" spans="3:17" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>17</v>
+      </c>
+      <c r="K1" s="4">
+        <v>77001</v>
       </c>
     </row>
     <row r="2" spans="3:17" x14ac:dyDescent="0.3">
@@ -590,16 +615,16 @@
       <c r="J3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="M3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="5" t="s">
         <v>25</v>
       </c>
       <c r="O3" s="3" t="s">
@@ -637,16 +662,16 @@
       <c r="J4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="M4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="5" t="s">
         <v>26</v>
       </c>
       <c r="O4" s="3" t="s">
@@ -684,16 +709,16 @@
       <c r="J5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="M5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="5" t="s">
         <v>24</v>
       </c>
       <c r="O5" s="3" t="s">
@@ -717,23 +742,29 @@
         <v>9</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
-      </c>
-      <c r="G6" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>3000</v>
+      </c>
       <c r="H6" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="3:17" x14ac:dyDescent="0.3">
@@ -758,10 +789,10 @@
       <c r="J7" s="1">
         <v>0</v>
       </c>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1">
@@ -790,10 +821,10 @@
       <c r="J8" s="1">
         <v>0</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1">
@@ -822,10 +853,10 @@
       <c r="J9" s="1">
         <v>0</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1">
@@ -854,10 +885,10 @@
       <c r="J10" s="1">
         <v>0</v>
       </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1">

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -176,11 +176,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>77001,77001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>100,200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>选中一个目标测试单体伤害</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>77001,77002</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -750,14 +754,17 @@
       <c r="H6" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="I6" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
   <si>
     <t>#</t>
   </si>
@@ -140,51 +140,55 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>int[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中自身Buff</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitBuffs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShapeParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>形状</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelectParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>selectParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,3000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,200</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>选中一个目标测试单体伤害</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>77001,77002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>HitBuffs</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>int[]</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>命中自身Buff</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SelfHitBuffs</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ShapeParam</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>形状</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SelectParam</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>selectParam</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,3000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>100,200</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>选中一个目标测试单体伤害</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>77001,77002</t>
+    <t>55001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -580,7 +584,7 @@
   <sheetData>
     <row r="1" spans="3:17" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>17</v>
@@ -608,10 +612,10 @@
         <v>14</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>4</v>
@@ -635,7 +639,7 @@
         <v>33</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>27</v>
@@ -655,10 +659,10 @@
         <v>16</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>5</v>
@@ -679,10 +683,10 @@
         <v>26</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>28</v>
@@ -726,10 +730,10 @@
         <v>24</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>15</v>
@@ -737,7 +741,7 @@
     </row>
     <row r="6" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
-        <v>6600001</v>
+        <v>66001</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -752,23 +756,25 @@
         <v>3000</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
-      <c r="O6" s="1"/>
+      <c r="O6" s="6" t="s">
+        <v>46</v>
+      </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1">
         <v>1000</v>
@@ -776,7 +782,7 @@
     </row>
     <row r="7" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
-        <v>6600002</v>
+        <v>66002</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -808,7 +814,7 @@
     </row>
     <row r="8" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
-        <v>6600003</v>
+        <v>66003</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -840,7 +846,7 @@
     </row>
     <row r="9" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
-        <v>6600004</v>
+        <v>66004</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -872,7 +878,7 @@
     </row>
     <row r="10" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
-        <v>6600005</v>
+        <v>66005</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A745C5-84B6-4206-98CE-08217368D092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13065"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CastProto" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
   <si>
     <t>#</t>
   </si>
@@ -189,13 +195,41 @@
   </si>
   <si>
     <t>55001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能开始特效</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能命中特效</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>施法转向</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NeedLookTarget</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -275,14 +309,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -320,7 +357,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -392,7 +429,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -565,8 +602,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C1:Q10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C1:T10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -578,11 +615,12 @@
     <col min="10" max="10" width="15.25" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="15.25" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="15.25" style="2" customWidth="1"/>
-    <col min="17" max="17" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="2"/>
+    <col min="17" max="19" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.25" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:20" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
         <v>40</v>
       </c>
@@ -593,12 +631,12 @@
         <v>77001</v>
       </c>
     </row>
-    <row r="2" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:20" x14ac:dyDescent="0.3">
       <c r="I2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -644,8 +682,17 @@
       <c r="Q3" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="R3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="4" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -691,8 +738,17 @@
       <c r="Q4" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="R4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="5" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -738,8 +794,17 @@
       <c r="Q5" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="R5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="T5" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="6" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>66001</v>
       </c>
@@ -777,10 +842,19 @@
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1">
-        <v>1000</v>
+        <v>300</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>66002</v>
       </c>
@@ -811,8 +885,15 @@
       <c r="Q7" s="1">
         <v>0</v>
       </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1">
+        <v>0</v>
+      </c>
+      <c r="T7" s="1"/>
     </row>
-    <row r="8" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>66003</v>
       </c>
@@ -843,8 +924,15 @@
       <c r="Q8" s="1">
         <v>0</v>
       </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1">
+        <v>0</v>
+      </c>
+      <c r="T8" s="1"/>
     </row>
-    <row r="9" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>66004</v>
       </c>
@@ -875,8 +963,15 @@
       <c r="Q9" s="1">
         <v>0</v>
       </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1">
+        <v>0</v>
+      </c>
+      <c r="T9" s="1"/>
     </row>
-    <row r="10" spans="3:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:20" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>66005</v>
       </c>
@@ -907,6 +1002,13 @@
       <c r="Q10" s="1">
         <v>0</v>
       </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8A745C5-84B6-4206-98CE-08217368D092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1A5D1F-29AE-487F-B256-7F3F60174A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
   <si>
     <t>#</t>
   </si>
@@ -223,6 +223,14 @@
   </si>
   <si>
     <t>NeedLookTarget</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能不可打断时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnBreakTime</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -603,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:T10"/>
+  <dimension ref="C1:U10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -614,13 +622,13 @@
     <col min="9" max="9" width="28.75" style="2" customWidth="1"/>
     <col min="10" max="10" width="15.25" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="15.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="15.25" style="2" customWidth="1"/>
-    <col min="17" max="19" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.25" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="15" max="17" width="15.25" style="2" customWidth="1"/>
+    <col min="18" max="20" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.25" style="2" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:21" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
         <v>40</v>
       </c>
@@ -631,12 +639,12 @@
         <v>77001</v>
       </c>
     </row>
-    <row r="2" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:21" x14ac:dyDescent="0.3">
       <c r="I2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -680,19 +688,22 @@
         <v>35</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -736,19 +747,22 @@
         <v>36</v>
       </c>
       <c r="Q4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -795,16 +809,19 @@
         <v>15</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="T5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>66001</v>
       </c>
@@ -842,19 +859,22 @@
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1">
+        <v>200</v>
+      </c>
+      <c r="R6" s="1">
         <v>300</v>
       </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
       <c r="S6" s="1">
         <v>0</v>
       </c>
-      <c r="T6" s="1" t="b">
+      <c r="T6" s="1">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>66002</v>
       </c>
@@ -891,9 +911,12 @@
       <c r="S7" s="1">
         <v>0</v>
       </c>
-      <c r="T7" s="1"/>
+      <c r="T7" s="1">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1"/>
     </row>
-    <row r="8" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>66003</v>
       </c>
@@ -930,9 +953,12 @@
       <c r="S8" s="1">
         <v>0</v>
       </c>
-      <c r="T8" s="1"/>
+      <c r="T8" s="1">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1"/>
     </row>
-    <row r="9" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>66004</v>
       </c>
@@ -969,9 +995,12 @@
       <c r="S9" s="1">
         <v>0</v>
       </c>
-      <c r="T9" s="1"/>
+      <c r="T9" s="1">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1"/>
     </row>
-    <row r="10" spans="3:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:21" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>66005</v>
       </c>
@@ -1008,7 +1037,10 @@
       <c r="S10" s="1">
         <v>0</v>
       </c>
-      <c r="T10" s="1"/>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1A5D1F-29AE-487F-B256-7F3F60174A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3468C70D-96FD-4260-B87F-B57F491A1160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1635" yWindow="3540" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CastProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
   <si>
     <t>#</t>
   </si>
@@ -231,6 +231,14 @@
   </si>
   <si>
     <t>UnBreakTime</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>22001,22001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -611,7 +619,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:U10"/>
+  <dimension ref="C1:V10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -623,12 +631,12 @@
     <col min="10" max="10" width="15.25" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="15.25" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="17" width="15.25" style="2" customWidth="1"/>
-    <col min="18" max="20" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.25" style="2" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="2"/>
+    <col min="18" max="21" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.25" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:22" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
         <v>40</v>
       </c>
@@ -639,12 +647,12 @@
         <v>77001</v>
       </c>
     </row>
-    <row r="2" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:22" x14ac:dyDescent="0.3">
       <c r="I2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -700,10 +708,13 @@
         <v>49</v>
       </c>
       <c r="U3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="V3" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -756,13 +767,16 @@
         <v>48</v>
       </c>
       <c r="T4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -818,10 +832,13 @@
         <v>18</v>
       </c>
       <c r="U5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>66001</v>
       </c>
@@ -870,11 +887,14 @@
       <c r="T6" s="1">
         <v>0</v>
       </c>
-      <c r="U6" s="1" t="b">
+      <c r="U6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="V6" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>66002</v>
       </c>
@@ -914,9 +934,12 @@
       <c r="T7" s="1">
         <v>0</v>
       </c>
-      <c r="U7" s="1"/>
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>66003</v>
       </c>
@@ -956,9 +979,12 @@
       <c r="T8" s="1">
         <v>0</v>
       </c>
-      <c r="U8" s="1"/>
+      <c r="U8" s="1">
+        <v>0</v>
+      </c>
+      <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>66004</v>
       </c>
@@ -998,9 +1024,12 @@
       <c r="T9" s="1">
         <v>0</v>
       </c>
-      <c r="U9" s="1"/>
+      <c r="U9" s="1">
+        <v>0</v>
+      </c>
+      <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="3:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:22" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>66005</v>
       </c>
@@ -1040,7 +1069,10 @@
       <c r="T10" s="1">
         <v>0</v>
       </c>
-      <c r="U10" s="1"/>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3468C70D-96FD-4260-B87F-B57F491A1160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A00AF54-3F82-4C8E-8B14-8BBC9DC7770F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1635" yWindow="3540" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,10 +174,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>0,3000</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>100,200</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -239,6 +235,10 @@
   </si>
   <si>
     <t>22001,22001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,2000</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -696,22 +696,22 @@
         <v>35</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="3:22" x14ac:dyDescent="0.3">
@@ -752,28 +752,28 @@
         <v>26</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>36</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="3:22" x14ac:dyDescent="0.3">
@@ -835,7 +835,7 @@
         <v>18</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="3:22" x14ac:dyDescent="0.3">
@@ -852,27 +852,27 @@
         <v>2</v>
       </c>
       <c r="G6" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J6" s="1">
         <v>2</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="6"/>
       <c r="O6" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P6" s="1"/>
       <c r="Q6" s="1">
@@ -888,7 +888,7 @@
         <v>0</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="V6" s="1" t="b">
         <v>1</v>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A00AF54-3F82-4C8E-8B14-8BBC9DC7770F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7541605-3807-4521-AA2B-2B6C126C9381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1635" yWindow="3540" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2400" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CastProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="70">
   <si>
     <t>#</t>
   </si>
@@ -239,6 +239,54 @@
   </si>
   <si>
     <t>0,2000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,5000</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>选中一个目标测试假子弹</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>77003,77002</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>200,500</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartAnimation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击起手动画</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击动画</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>HitAnimation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>自己受击动画</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SelfHitAnimation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,22001</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -619,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:V10"/>
+  <dimension ref="C1:Y10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -632,27 +680,33 @@
     <col min="11" max="14" width="15.25" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="17" width="15.25" style="2" customWidth="1"/>
     <col min="18" max="21" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.25" style="2" customWidth="1"/>
-    <col min="23" max="16384" width="9" style="2"/>
+    <col min="22" max="25" width="15.25" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:25" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
         <v>40</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="4">
-        <v>77001</v>
-      </c>
     </row>
-    <row r="2" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:25" x14ac:dyDescent="0.3">
       <c r="I2" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="W2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y2" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="3" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -713,8 +767,17 @@
       <c r="V3" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="W3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="4" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -775,8 +838,17 @@
       <c r="V4" s="3" t="s">
         <v>52</v>
       </c>
+      <c r="W4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
-    <row r="5" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -837,8 +909,17 @@
       <c r="V5" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="W5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y5" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="6" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>66001</v>
       </c>
@@ -893,8 +974,17 @@
       <c r="V6" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="W6" s="1">
+        <v>3</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="7" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>66002</v>
       </c>
@@ -910,36 +1000,54 @@
       <c r="G7" s="1">
         <v>5000</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
+      <c r="H7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+        <v>2</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6"/>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="R7" s="1">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="S7" s="1">
-        <v>0</v>
+        <v>22003</v>
       </c>
       <c r="T7" s="1">
         <v>0</v>
       </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1"/>
+      <c r="U7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" s="1">
+        <v>3</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="8" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>66003</v>
       </c>
@@ -983,8 +1091,17 @@
         <v>0</v>
       </c>
       <c r="V8" s="1"/>
+      <c r="W8" s="1">
+        <v>3</v>
+      </c>
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="9" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>66004</v>
       </c>
@@ -1028,8 +1145,17 @@
         <v>0</v>
       </c>
       <c r="V9" s="1"/>
+      <c r="W9" s="1">
+        <v>3</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="3:22" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:25" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>66005</v>
       </c>
@@ -1073,6 +1199,15 @@
         <v>0</v>
       </c>
       <c r="V10" s="1"/>
+      <c r="W10" s="1">
+        <v>3</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7541605-3807-4521-AA2B-2B6C126C9381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2400" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1335" yWindow="2325" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CastProto" sheetId="1" r:id="rId1"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/CastConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git\FAE\ETMMO\ET-release8.1\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7541605-3807-4521-AA2B-2B6C126C9381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BE746F-4530-43D3-8EC5-0D451AA1BBC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="2325" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="645" yWindow="2505" windowWidth="24630" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CastProto" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="73">
   <si>
     <t>#</t>
   </si>
@@ -287,6 +287,18 @@
   </si>
   <si>
     <t>0,22001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能冷却</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CoolDown</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&gt;=0才会打断逻辑，-1表示无视打断逻辑也不会被打断</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -667,7 +679,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:Y10"/>
+  <dimension ref="C1:Z10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -678,26 +690,27 @@
     <col min="9" max="9" width="28.75" style="2" customWidth="1"/>
     <col min="10" max="10" width="15.25" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="14" width="15.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="15.25" style="2" customWidth="1"/>
-    <col min="18" max="21" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="15.25" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="2"/>
+    <col min="15" max="16" width="15.25" style="2" customWidth="1"/>
+    <col min="17" max="17" width="40.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="15.25" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:26" x14ac:dyDescent="0.3">
       <c r="G1" s="2" t="s">
         <v>40</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="Q1" s="2" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="2" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:26" x14ac:dyDescent="0.3">
       <c r="I2" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="X2" s="2" t="s">
         <v>66</v>
@@ -705,8 +718,11 @@
       <c r="Y2" s="2" t="s">
         <v>66</v>
       </c>
+      <c r="Z2" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="3" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -756,28 +772,31 @@
         <v>27</v>
       </c>
       <c r="S3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="U3" s="3" t="s">
         <v>48</v>
       </c>
       <c r="V3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="W3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="X3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="Y3" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="Y3" s="3" t="s">
+      <c r="Z3" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -827,28 +846,31 @@
         <v>28</v>
       </c>
       <c r="S4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="T4" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="U4" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="U4" s="3" t="s">
+      <c r="V4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="V4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="W4" s="3" t="s">
+      <c r="X4" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="X4" s="3" t="s">
+      <c r="Y4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -898,7 +920,7 @@
         <v>15</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>18</v>
@@ -907,10 +929,10 @@
         <v>18</v>
       </c>
       <c r="V5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W5" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="W5" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="X5" s="3" t="s">
         <v>15</v>
@@ -918,8 +940,11 @@
       <c r="Y5" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="Z5" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="6" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>66001</v>
       </c>
@@ -963,28 +988,31 @@
         <v>300</v>
       </c>
       <c r="S6" s="1">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
-      <c r="U6" s="6" t="s">
+      <c r="U6" s="1">
+        <v>0</v>
+      </c>
+      <c r="V6" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="V6" s="1" t="b">
+      <c r="W6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="W6" s="1">
+      <c r="X6" s="1">
         <v>3</v>
       </c>
-      <c r="X6" s="1">
-        <v>0</v>
-      </c>
       <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>66002</v>
       </c>
@@ -1026,28 +1054,31 @@
         <v>500</v>
       </c>
       <c r="S7" s="1">
+        <v>3000</v>
+      </c>
+      <c r="T7" s="1">
         <v>22003</v>
       </c>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6" t="s">
+      <c r="U7" s="1">
+        <v>0</v>
+      </c>
+      <c r="V7" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="V7" s="1" t="b">
+      <c r="W7" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="W7" s="1">
+      <c r="X7" s="1">
         <v>3</v>
       </c>
-      <c r="X7" s="1">
-        <v>0</v>
-      </c>
       <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>66003</v>
       </c>
@@ -1090,18 +1121,21 @@
       <c r="U8" s="1">
         <v>0</v>
       </c>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1">
+      <c r="V8" s="1">
+        <v>0</v>
+      </c>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1">
         <v>3</v>
       </c>
-      <c r="X8" s="1">
-        <v>0</v>
-      </c>
       <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>66004</v>
       </c>
@@ -1144,18 +1178,21 @@
       <c r="U9" s="1">
         <v>0</v>
       </c>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1">
+      <c r="V9" s="1">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1">
         <v>3</v>
       </c>
-      <c r="X9" s="1">
-        <v>0</v>
-      </c>
       <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="3:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C10" s="1">
         <v>66005</v>
       </c>
@@ -1198,14 +1235,17 @@
       <c r="U10" s="1">
         <v>0</v>
       </c>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1">
+      <c r="V10" s="1">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1">
         <v>3</v>
       </c>
-      <c r="X10" s="1">
-        <v>0</v>
-      </c>
       <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
         <v>5</v>
       </c>
     </row>
